--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444969144207771</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>35691876</v>
+        <v>4031492</v>
       </c>
       <c r="L2" t="n">
-        <v>19711686</v>
+        <v>1961810</v>
       </c>
       <c r="M2" t="n">
-        <v>4710089</v>
+        <v>428102</v>
       </c>
       <c r="N2" t="n">
-        <v>142719</v>
+        <v>10540</v>
       </c>
       <c r="O2" t="n">
-        <v>2853095</v>
+        <v>274007</v>
       </c>
       <c r="P2" t="n">
-        <v>1008107</v>
+        <v>101318</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8669537305831909</v>
+        <v>0.7820428609848022</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7501139044761658</v>
+        <v>0.5984733700752258</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6831796169281006</v>
+        <v>0.4958430826663971</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2409467101097107</v>
+        <v>0.1448558270931244</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7151691317558289</v>
+        <v>0.550411581993103</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8357343077659607</v>
+        <v>0.679216206073761</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024809124862332</v>
       </c>
       <c r="C3" t="n">
-        <v>2896</v>
+        <v>362</v>
       </c>
       <c r="D3" t="n">
-        <v>35691876</v>
+        <v>4031492</v>
       </c>
       <c r="E3" t="n">
-        <v>4327603</v>
+        <v>915073</v>
       </c>
       <c r="F3" t="n">
-        <v>102835</v>
+        <v>36243</v>
       </c>
       <c r="G3" t="n">
-        <v>7129</v>
+        <v>2222</v>
       </c>
       <c r="H3" t="n">
-        <v>7408</v>
+        <v>3154</v>
       </c>
       <c r="I3" t="n">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="J3" t="n">
-        <v>80129896</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>85019406</v>
+        <v>10217330</v>
       </c>
       <c r="L3" t="n">
-        <v>97886365</v>
+        <v>11717475</v>
       </c>
       <c r="M3" t="n">
-        <v>120981707</v>
+        <v>14956380</v>
       </c>
       <c r="N3" t="n">
-        <v>129473134</v>
+        <v>16177774</v>
       </c>
       <c r="O3" t="n">
-        <v>125423356</v>
+        <v>15594892</v>
       </c>
       <c r="P3" t="n">
-        <v>128891532</v>
+        <v>16088159</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88918536901474</v>
+        <v>0.8081273436546326</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7528180480003357</v>
+        <v>0.5952253937721252</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6304649710655212</v>
+        <v>0.4564279019832611</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1998700350522995</v>
+        <v>0.1176286786794662</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6997784972190857</v>
+        <v>0.5363295078277588</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6516014933586121</v>
+        <v>0.5233638286590576</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5123463</v>
+        <v>1041366</v>
       </c>
       <c r="E4" t="n">
-        <v>19711686</v>
+        <v>1961810</v>
       </c>
       <c r="F4" t="n">
-        <v>1176865</v>
+        <v>239636</v>
       </c>
       <c r="G4" t="n">
-        <v>43264</v>
+        <v>11772</v>
       </c>
       <c r="H4" t="n">
-        <v>118561</v>
+        <v>37485</v>
       </c>
       <c r="I4" t="n">
-        <v>10025</v>
+        <v>3842</v>
       </c>
       <c r="J4" t="n">
-        <v>3080</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>5477421</v>
+        <v>1123586</v>
       </c>
       <c r="L4" t="n">
-        <v>6566571</v>
+        <v>1316214</v>
       </c>
       <c r="M4" t="n">
-        <v>2184275</v>
+        <v>435280</v>
       </c>
       <c r="N4" t="n">
-        <v>449607</v>
+        <v>62222</v>
       </c>
       <c r="O4" t="n">
-        <v>1136304</v>
+        <v>223815</v>
       </c>
       <c r="P4" t="n">
-        <v>198146</v>
+        <v>47851</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8779288530349731</v>
+        <v>0.7948711514472961</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7514635324478149</v>
+        <v>0.5968449115753174</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6557645797729492</v>
+        <v>0.4753197729587555</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2184945344924927</v>
+        <v>0.1298301517963409</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7073900699615479</v>
+        <v>0.5432793498039246</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7322700619697571</v>
+        <v>0.5911909341812134</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>240173</v>
+        <v>59937</v>
       </c>
       <c r="E5" t="n">
-        <v>1890321</v>
+        <v>318768</v>
       </c>
       <c r="F5" t="n">
-        <v>4710089</v>
+        <v>428102</v>
       </c>
       <c r="G5" t="n">
-        <v>133873</v>
+        <v>20932</v>
       </c>
       <c r="H5" t="n">
-        <v>456657</v>
+        <v>98402</v>
       </c>
       <c r="I5" t="n">
-        <v>39705</v>
+        <v>11799</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4448097</v>
+        <v>957192</v>
       </c>
       <c r="L5" t="n">
-        <v>6472178</v>
+        <v>1334101</v>
       </c>
       <c r="M5" t="n">
-        <v>2760729</v>
+        <v>509838</v>
       </c>
       <c r="N5" t="n">
-        <v>571340</v>
+        <v>79064</v>
       </c>
       <c r="O5" t="n">
-        <v>1224045</v>
+        <v>236886</v>
       </c>
       <c r="P5" t="n">
-        <v>539015</v>
+        <v>92272</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9240220189094543</v>
+        <v>0.8725762963294983</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9001908302307129</v>
+        <v>0.8376986980438232</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9621469378471375</v>
+        <v>0.9421223998069763</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9921848177909851</v>
+        <v>0.9913478493690491</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9819319844245911</v>
+        <v>0.9717873930931091</v>
       </c>
       <c r="W5" t="n">
-        <v>0.994357168674469</v>
+        <v>0.9914190769195557</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>103349</v>
+        <v>16961</v>
       </c>
       <c r="E6" t="n">
-        <v>160724</v>
+        <v>22926</v>
       </c>
       <c r="F6" t="n">
-        <v>224307</v>
+        <v>25605</v>
       </c>
       <c r="G6" t="n">
-        <v>142719</v>
+        <v>10540</v>
       </c>
       <c r="H6" t="n">
-        <v>77405</v>
+        <v>12096</v>
       </c>
       <c r="I6" t="n">
-        <v>5389</v>
+        <v>1455</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>9970</v>
+        <v>5210</v>
       </c>
       <c r="E7" t="n">
-        <v>174722</v>
+        <v>54233</v>
       </c>
       <c r="F7" t="n">
-        <v>644193</v>
+        <v>122399</v>
       </c>
       <c r="G7" t="n">
-        <v>252359</v>
+        <v>24427</v>
       </c>
       <c r="H7" t="n">
-        <v>2853095</v>
+        <v>274007</v>
       </c>
       <c r="I7" t="n">
-        <v>142801</v>
+        <v>30617</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>112</v>
       </c>
       <c r="E8" t="n">
-        <v>13201</v>
+        <v>5214</v>
       </c>
       <c r="F8" t="n">
-        <v>36075</v>
+        <v>11397</v>
       </c>
       <c r="G8" t="n">
-        <v>12982</v>
+        <v>2869</v>
       </c>
       <c r="H8" t="n">
-        <v>476273</v>
+        <v>72678</v>
       </c>
       <c r="I8" t="n">
-        <v>1008107</v>
+        <v>101318</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
